--- a/public/crawlability-improvisrael-september-2026.xlsx
+++ b/public/crawlability-improvisrael-september-2026.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>להסיר 1 רשומות כפולות ממפת האתר.</t>
+          <t>להסיר רשומה כפולה אחת ממפת האתר.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-improvisrael-september-2026.xlsx
+++ b/public/crawlability-improvisrael-september-2026.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום פעולות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -91,13 +85,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -501,22 +492,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת שמפנה ולהשאיר את כתובת היעד בלבד.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>להסיר רשומה כפולה אחת ממפת האתר.</t>
+          <t>להסיר ממפת האתר כתובת אחת שמפנה (באתר WordPress/Yoast: להעביר את העמודים המפנים לטיוטה או להחריגם מה-sitemap; המפה נוצרת אוטומטית).</t>
         </is>
       </c>
     </row>
@@ -526,134 +502,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>כתובת</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בסריקה 23.09</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בבדיקה חיה 27.09</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>יעד סופי / יעד להפניה</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>קפיצות</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>קישורים נכנסים</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>עמודי מקור (עד 10)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>סוג</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה נדרשת</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>יעד מומלץ להפניית 301</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>https://improvisrael.co.il/</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>403</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>https://improvisrael.co.il/
-https://improvisrael.co.il/improv-benefits/</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 403); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -719,7 +567,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/sitemap_index.xml</t>
         </is>
@@ -773,7 +621,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/sitemap_index.xml</t>
         </is>
@@ -795,7 +643,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/post-sitemap.xml</t>
         </is>
@@ -817,7 +665,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/page-sitemap.xml</t>
         </is>
@@ -839,7 +687,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/product-sitemap.xml</t>
         </is>
@@ -861,7 +709,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/course_card-sitemap.xml</t>
         </is>
@@ -883,7 +731,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/events-sitemap.xml</t>
         </is>
@@ -905,7 +753,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/category-sitemap.xml</t>
         </is>
@@ -927,7 +775,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/post_tag-sitemap.xml</t>
         </is>
@@ -949,7 +797,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/product_cat-sitemap.xml</t>
         </is>
@@ -971,7 +819,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/product_tag-sitemap.xml</t>
         </is>
@@ -993,7 +841,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/author-sitemap.xml</t>
         </is>
@@ -1015,7 +863,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/sitemap.xml</t>
         </is>
@@ -1037,7 +885,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/wp-sitemap.xml</t>
         </is>
@@ -1081,12 +929,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/checkout/</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/cart/</t>
         </is>
@@ -1103,7 +951,7 @@
           <t>קוד 403 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/</t>
         </is>
@@ -1116,7 +964,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/</t>
         </is>
@@ -1126,7 +974,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (0 הפניות)</t>
         </is>
@@ -1138,7 +986,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>http://improvisrael.co.il/</t>
         </is>
@@ -1148,7 +996,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (1 הפניות)</t>
         </is>
@@ -1160,7 +1008,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>https://www.improvisrael.co.il/</t>
         </is>
@@ -1170,7 +1018,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (1 הפניות)</t>
         </is>
@@ -1182,7 +1030,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>http://www.improvisrael.co.il/</t>
         </is>
@@ -1192,7 +1040,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (2 הפניות)</t>
         </is>
@@ -1245,7 +1093,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/</t>
         </is>
@@ -1257,7 +1105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1357,7 +1205,7 @@
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
@@ -1380,7 +1228,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>https://berlin.improvisrael.co.il</t>
         </is>
@@ -1400,7 +1248,7 @@
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
@@ -1411,7 +1259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/crawlability-improvisrael-september-2026.xlsx
+++ b/public/crawlability-improvisrael-september-2026.xlsx
@@ -39,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -85,10 +90,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -456,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -493,6 +501,21 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>להסיר ממפת האתר כתובת אחת שמפנה (באתר WordPress/Yoast: להעביר את העמודים המפנים לטיוטה או להחריגם מה-sitemap; המפה נוצרת אוטומטית).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>לסרוק מחדש את האתר (הסריקה מ-23.09 נעצרה בעמוד הבית עם 403).</t>
         </is>
       </c>
     </row>
@@ -567,7 +590,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/sitemap_index.xml</t>
         </is>
@@ -621,7 +644,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/sitemap_index.xml</t>
         </is>
@@ -643,7 +666,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/post-sitemap.xml</t>
         </is>
@@ -665,7 +688,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/page-sitemap.xml</t>
         </is>
@@ -687,7 +710,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/product-sitemap.xml</t>
         </is>
@@ -709,7 +732,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/course_card-sitemap.xml</t>
         </is>
@@ -731,7 +754,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/events-sitemap.xml</t>
         </is>
@@ -753,7 +776,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/category-sitemap.xml</t>
         </is>
@@ -775,7 +798,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/post_tag-sitemap.xml</t>
         </is>
@@ -797,7 +820,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/product_cat-sitemap.xml</t>
         </is>
@@ -819,7 +842,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/product_tag-sitemap.xml</t>
         </is>
@@ -841,7 +864,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/author-sitemap.xml</t>
         </is>
@@ -863,7 +886,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/sitemap.xml</t>
         </is>
@@ -885,7 +908,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/wp-sitemap.xml</t>
         </is>
@@ -929,12 +952,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/checkout/</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/cart/</t>
         </is>
@@ -951,7 +974,7 @@
           <t>קוד 403 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/</t>
         </is>
@@ -964,7 +987,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/</t>
         </is>
@@ -974,7 +997,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (0 הפניות)</t>
         </is>
@@ -986,7 +1009,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>http://improvisrael.co.il/</t>
         </is>
@@ -996,7 +1019,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (1 הפניות)</t>
         </is>
@@ -1008,7 +1031,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>https://www.improvisrael.co.il/</t>
         </is>
@@ -1018,7 +1041,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (1 הפניות)</t>
         </is>
@@ -1030,7 +1053,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>http://www.improvisrael.co.il/</t>
         </is>
@@ -1040,7 +1063,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/ (2 הפניות)</t>
         </is>
@@ -1093,7 +1116,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>https://improvisrael.co.il/</t>
         </is>
@@ -1205,7 +1228,7 @@
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
@@ -1228,7 +1251,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>https://berlin.improvisrael.co.il</t>
         </is>
@@ -1248,7 +1271,7 @@
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
